--- a/data/trans_orig/P1801_2016_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1801_2016_2023-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>407254</t>
+          <t>408665</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>459859</t>
+          <t>461890</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>620310</t>
+          <t>624345</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>684767</t>
+          <t>684699</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1044132</t>
+          <t>1042617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1126294</t>
+          <t>1127780</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,48%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>294488</t>
+          <t>292457</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>347093</t>
+          <t>345682</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>309893</t>
+          <t>309961</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>374350</t>
+          <t>370315</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>622713</t>
+          <t>621227</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>704875</t>
+          <t>706390</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,39%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>859091</t>
+          <t>856725</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>946238</t>
+          <t>952943</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1024032</t>
+          <t>1027815</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1113701</t>
+          <t>1118903</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1913676</t>
+          <t>1910625</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2041236</t>
+          <t>2038786</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,16%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1130147</t>
+          <t>1123442</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1217294</t>
+          <t>1219660</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>874599</t>
+          <t>869397</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>964268</t>
+          <t>960485</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2023449</t>
+          <t>2025899</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2151009</t>
+          <t>2154060</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,99%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>206044</t>
+          <t>206898</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>253563</t>
+          <t>253311</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>273108</t>
+          <t>272758</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>321450</t>
+          <t>320143</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>491555</t>
+          <t>489449</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>561074</t>
+          <t>560156</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,11%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>293323</t>
+          <t>293575</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>340842</t>
+          <t>339988</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>227690</t>
+          <t>228997</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>276032</t>
+          <t>276382</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>534953</t>
+          <t>535871</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>604472</t>
+          <t>606578</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,34%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1504686</t>
+          <t>1506277</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1619619</t>
+          <t>1625765</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1960129</t>
+          <t>1960156</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2084021</t>
+          <t>2079120</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3502469</t>
+          <t>3506054</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3668338</t>
+          <t>3670646</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,12%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1757999</t>
+          <t>1751853</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1872932</t>
+          <t>1871341</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1448079</t>
+          <t>1452980</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1571971</t>
+          <t>1571944</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3241380</t>
+          <t>3239072</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3407249</t>
+          <t>3403664</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,26%</t>
         </is>
       </c>
     </row>
@@ -2329,32 +2329,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>303393</t>
+          <t>322861</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>281144</t>
+          <t>298440</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>323704</t>
+          <t>346386</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2364,32 +2364,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>484577</t>
+          <t>526907</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>463373</t>
+          <t>507076</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>505754</t>
+          <t>549005</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2399,32 +2399,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>787970</t>
+          <t>849767</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>759484</t>
+          <t>820059</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>817582</t>
+          <t>884847</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>63,28%</t>
         </is>
       </c>
     </row>
@@ -2442,32 +2442,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>210555</t>
+          <t>254598</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>190244</t>
+          <t>231073</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>232804</t>
+          <t>279019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2477,32 +2477,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>269849</t>
+          <t>293997</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248672</t>
+          <t>271899</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>291053</t>
+          <t>313828</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2512,32 +2512,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>480404</t>
+          <t>548596</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>450792</t>
+          <t>513516</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>508890</t>
+          <t>578304</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>41,36%</t>
         </is>
       </c>
     </row>
@@ -2555,17 +2555,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513948</t>
+          <t>577459</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513948</t>
+          <t>577459</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513948</t>
+          <t>577459</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2590,17 +2590,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>754426</t>
+          <t>820904</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>754426</t>
+          <t>820904</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>754426</t>
+          <t>820904</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2625,17 +2625,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1268374</t>
+          <t>1398363</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1268374</t>
+          <t>1398363</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1268374</t>
+          <t>1398363</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2672,32 +2672,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1163660</t>
+          <t>984435</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1007851</t>
+          <t>930030</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1473224</t>
+          <t>1039968</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2707,32 +2707,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1201306</t>
+          <t>1109857</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1052424</t>
+          <t>1066473</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1465283</t>
+          <t>1150128</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2742,32 +2742,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2364966</t>
+          <t>2094292</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2130326</t>
+          <t>2021573</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2809090</t>
+          <t>2155903</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>49,05%</t>
         </is>
       </c>
     </row>
@@ -2785,32 +2785,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1124342</t>
+          <t>1243926</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>814778</t>
+          <t>1188393</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1280151</t>
+          <t>1298331</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2820,32 +2820,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1033970</t>
+          <t>1057416</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>769993</t>
+          <t>1017145</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1182852</t>
+          <t>1100800</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2855,32 +2855,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2158312</t>
+          <t>2301341</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1714188</t>
+          <t>2239730</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2392952</t>
+          <t>2374060</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>54,01%</t>
         </is>
       </c>
     </row>
@@ -2898,17 +2898,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288002</t>
+          <t>2228361</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288002</t>
+          <t>2228361</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288002</t>
+          <t>2228361</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2933,17 +2933,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2235276</t>
+          <t>2167273</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2235276</t>
+          <t>2167273</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2235276</t>
+          <t>2167273</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2968,17 +2968,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4523278</t>
+          <t>4395633</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4523278</t>
+          <t>4395633</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4523278</t>
+          <t>4395633</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3015,32 +3015,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>357015</t>
+          <t>380451</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>327962</t>
+          <t>353151</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>386850</t>
+          <t>409925</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3050,32 +3050,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>395007</t>
+          <t>442280</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>371117</t>
+          <t>416563</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>416426</t>
+          <t>466339</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3085,32 +3085,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>752022</t>
+          <t>822731</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>714050</t>
+          <t>781673</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>786883</t>
+          <t>863083</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>59,76%</t>
         </is>
       </c>
     </row>
@@ -3128,32 +3128,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>289608</t>
+          <t>331136</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>259773</t>
+          <t>301662</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318661</t>
+          <t>358436</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3163,32 +3163,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>263234</t>
+          <t>290368</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>241815</t>
+          <t>266309</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>287124</t>
+          <t>316085</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3198,32 +3198,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>552842</t>
+          <t>621504</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>517981</t>
+          <t>581152</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>590814</t>
+          <t>662562</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,88%</t>
         </is>
       </c>
     </row>
@@ -3241,17 +3241,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3276,17 +3276,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>658241</t>
+          <t>732648</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>658241</t>
+          <t>732648</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>658241</t>
+          <t>732648</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1304864</t>
+          <t>1444235</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1304864</t>
+          <t>1444235</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1304864</t>
+          <t>1444235</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3358,32 +3358,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1824068</t>
+          <t>1687746</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1679422</t>
+          <t>1628035</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2211757</t>
+          <t>1759284</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3393,32 +3393,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2080889</t>
+          <t>2079043</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1940116</t>
+          <t>2021992</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2381337</t>
+          <t>2131967</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3428,32 +3428,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3904958</t>
+          <t>3766790</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3660270</t>
+          <t>3687153</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4323540</t>
+          <t>3853892</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>53,24%</t>
         </is>
       </c>
     </row>
@@ -3471,32 +3471,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1624505</t>
+          <t>1829661</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1236816</t>
+          <t>1758123</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1769151</t>
+          <t>1889372</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1567053</t>
+          <t>1641781</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1266605</t>
+          <t>1588857</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1707826</t>
+          <t>1698832</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3191558</t>
+          <t>3471441</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2772976</t>
+          <t>3384339</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3436246</t>
+          <t>3551078</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>49,06%</t>
         </is>
       </c>
     </row>
@@ -3584,17 +3584,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3448573</t>
+          <t>3517407</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3448573</t>
+          <t>3517407</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3448573</t>
+          <t>3517407</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3619,17 +3619,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3647942</t>
+          <t>3720824</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3647942</t>
+          <t>3720824</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3647942</t>
+          <t>3720824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3654,17 +3654,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7096516</t>
+          <t>7238231</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7096516</t>
+          <t>7238231</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7096516</t>
+          <t>7238231</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
